--- a/diagramas/Libro2.xlsx
+++ b/diagramas/Libro2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universidaddeburgos-my.sharepoint.com/personal/mmm1059_alu_ubu_es/Documents/Escritorio/TFG-Marina-Martin/diagramas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="8_{4FCC31AE-55C1-4CE4-B909-C81D660EA50D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D683572A-7F85-4E0C-9C1C-F16047B1C2D7}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="8_{4FCC31AE-55C1-4CE4-B909-C81D660EA50D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E4D7528-E2E7-4D00-9DD2-7E2BBB79C13D}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{28BE8028-781D-4881-B67A-D6488C875A24}"/>
+    <workbookView minimized="1" xWindow="9696" yWindow="456" windowWidth="10164" windowHeight="9780" activeTab="1" xr2:uid="{28BE8028-781D-4881-B67A-D6488C875A24}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -282,6 +282,45 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -316,80 +355,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <fill>
         <patternFill>
@@ -457,6 +429,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -784,35 +760,35 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="26">
+      <c r="C2" s="34"/>
+      <c r="D2" s="39">
         <v>45566</v>
       </c>
-      <c r="E2" s="27"/>
+      <c r="E2" s="40"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="25"/>
-      <c r="D3" s="28">
+      <c r="C3" s="38"/>
+      <c r="D3" s="41">
         <v>45816</v>
       </c>
-      <c r="E3" s="29"/>
+      <c r="E3" s="42"/>
     </row>
     <row r="4" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="23"/>
-      <c r="D4" s="30">
+      <c r="C4" s="36"/>
+      <c r="D4" s="43">
         <f>D3-D2</f>
         <v>250</v>
       </c>
-      <c r="E4" s="31"/>
+      <c r="E4" s="44"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
@@ -960,23 +936,23 @@
     <mergeCell ref="D4:E4"/>
   </mergeCells>
   <conditionalFormatting sqref="D7:L12">
-    <cfRule type="expression" dxfId="8" priority="2">
+    <cfRule type="expression" priority="1">
+      <formula>AND(D$6&gt;=$B7,D$6&lt;=$C7)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="2">
       <formula>AND(D$6&gt;=$B7,D$6&lt;=$C7)</formula>
     </cfRule>
     <cfRule type="expression" priority="3">
       <formula>AND(D$6&gt;=$B6,D$6&lt;=$C6)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="4">
+    <cfRule type="expression" dxfId="6" priority="4">
       <formula>AND(D$6&gt;=$B6,D$6&lt;=$C6)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="6">
+    <cfRule type="expression" dxfId="5" priority="6">
       <formula>"'=AND(D$6&gt;=B$7,D$6&lt;=C$7)"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="10">
+    <cfRule type="expression" dxfId="4" priority="10">
       <formula>"(D$6&gt;=B$7,D$6&lt;=C$7)"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="1">
-      <formula>AND(D$6&gt;=$B7,D$6&lt;=$C7)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1004,44 +980,44 @@
       <c r="C1" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="33">
+      <c r="D1" s="21">
         <v>45931</v>
       </c>
-      <c r="E1" s="33">
+      <c r="E1" s="21">
         <f>D1+31</f>
         <v>45962</v>
       </c>
-      <c r="F1" s="33">
+      <c r="F1" s="21">
         <f>E1+30</f>
         <v>45992</v>
       </c>
-      <c r="G1" s="33">
+      <c r="G1" s="21">
         <f>F1+31</f>
         <v>46023</v>
       </c>
-      <c r="H1" s="33">
+      <c r="H1" s="21">
         <f>G1+31</f>
         <v>46054</v>
       </c>
-      <c r="I1" s="33">
+      <c r="I1" s="21">
         <f>H1+28</f>
         <v>46082</v>
       </c>
-      <c r="J1" s="33">
+      <c r="J1" s="21">
         <f>I1+31</f>
         <v>46113</v>
       </c>
-      <c r="K1" s="33">
+      <c r="K1" s="21">
         <f>J1+30</f>
         <v>46143</v>
       </c>
-      <c r="L1" s="34">
+      <c r="L1" s="22">
         <f>K1+31</f>
         <v>46174</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="23" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="2">
@@ -1050,18 +1026,18 @@
       <c r="C2" s="2">
         <v>45613</v>
       </c>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="38"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="26"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="27" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="1">
@@ -1070,58 +1046,58 @@
       <c r="C3" s="1">
         <v>45703</v>
       </c>
-      <c r="D3" s="40"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
       <c r="L3" s="18"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="39" t="s">
+      <c r="A4" s="27" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="1">
         <v>45667</v>
       </c>
       <c r="C4" s="1">
-        <v>45731</v>
-      </c>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="40"/>
-      <c r="K4" s="40"/>
+        <v>45769</v>
+      </c>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="28"/>
       <c r="L4" s="18"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="39" t="s">
+      <c r="A5" s="27" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="1">
         <v>45731</v>
       </c>
       <c r="C5" s="1">
-        <v>45767</v>
-      </c>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="40"/>
+        <v>45777</v>
+      </c>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="28"/>
       <c r="L5" s="18"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="39" t="s">
+      <c r="A6" s="27" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="1">
@@ -1130,24 +1106,24 @@
       <c r="C6" s="1">
         <v>45807</v>
       </c>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="41"/>
-      <c r="K6" s="41"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="29"/>
       <c r="L6" s="18"/>
     </row>
     <row r="7" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="42" t="s">
+      <c r="A7" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="32">
+      <c r="B7" s="20">
         <v>45748</v>
       </c>
-      <c r="C7" s="32">
+      <c r="C7" s="20">
         <v>45816</v>
       </c>
       <c r="D7" s="19"/>
@@ -1156,9 +1132,9 @@
       <c r="G7" s="19"/>
       <c r="H7" s="19"/>
       <c r="I7" s="19"/>
-      <c r="J7" s="43"/>
-      <c r="K7" s="43"/>
-      <c r="L7" s="44"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="32"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:L7">
